--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1312"/>
+  <dimension ref="A1:F1313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26664,7 +26664,27 @@
         <v>42.93999862670898</v>
       </c>
       <c r="F1312" t="n">
-        <v>225190</v>
+        <v>226465</v>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B1313" t="n">
+        <v>41.86</v>
+      </c>
+      <c r="C1313" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="D1313" t="n">
+        <v>41.84</v>
+      </c>
+      <c r="E1313" t="n">
+        <v>42.38</v>
+      </c>
+      <c r="F1313" t="n">
+        <v>56730</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -26672,19 +26672,19 @@
         <v>46231</v>
       </c>
       <c r="B1313" t="n">
-        <v>41.86</v>
+        <v>42.41</v>
       </c>
       <c r="C1313" t="n">
-        <v>42.6</v>
+        <v>42.64</v>
       </c>
       <c r="D1313" t="n">
-        <v>41.84</v>
+        <v>41.77</v>
       </c>
       <c r="E1313" t="n">
         <v>42.38</v>
       </c>
       <c r="F1313" t="n">
-        <v>56730</v>
+        <v>192089</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -26672,7 +26672,7 @@
         <v>46231</v>
       </c>
       <c r="B1313" t="n">
-        <v>42.41</v>
+        <v>42.47</v>
       </c>
       <c r="C1313" t="n">
         <v>42.64</v>
@@ -26684,7 +26684,7 @@
         <v>42.38</v>
       </c>
       <c r="F1313" t="n">
-        <v>192089</v>
+        <v>231308</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -26672,16 +26672,16 @@
         <v>46231</v>
       </c>
       <c r="B1313" t="n">
-        <v>42.47</v>
+        <v>42.47000122070312</v>
       </c>
       <c r="C1313" t="n">
-        <v>42.64</v>
+        <v>42.63999938964844</v>
       </c>
       <c r="D1313" t="n">
-        <v>41.77</v>
+        <v>41.81000137329102</v>
       </c>
       <c r="E1313" t="n">
-        <v>42.38</v>
+        <v>42.38000106811523</v>
       </c>
       <c r="F1313" t="n">
         <v>231308</v>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1313"/>
+  <dimension ref="A1:F1314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26687,6 +26687,26 @@
         <v>231308</v>
       </c>
     </row>
+    <row r="1314">
+      <c r="A1314" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B1314" t="n">
+        <v>42.57</v>
+      </c>
+      <c r="C1314" t="n">
+        <v>42.88</v>
+      </c>
+      <c r="D1314" t="n">
+        <v>42.31</v>
+      </c>
+      <c r="E1314" t="n">
+        <v>42.88</v>
+      </c>
+      <c r="F1314" t="n">
+        <v>111632</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -26692,19 +26692,19 @@
         <v>46232</v>
       </c>
       <c r="B1314" t="n">
-        <v>42.57</v>
+        <v>41.76</v>
       </c>
       <c r="C1314" t="n">
         <v>42.88</v>
       </c>
       <c r="D1314" t="n">
-        <v>42.31</v>
+        <v>41.76</v>
       </c>
       <c r="E1314" t="n">
         <v>42.88</v>
       </c>
       <c r="F1314" t="n">
-        <v>111632</v>
+        <v>174276</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1314"/>
+  <dimension ref="A1:F1315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26692,19 +26692,39 @@
         <v>46232</v>
       </c>
       <c r="B1314" t="n">
-        <v>41.76</v>
+        <v>41.7599983215332</v>
       </c>
       <c r="C1314" t="n">
-        <v>42.88</v>
+        <v>42.88000106811523</v>
       </c>
       <c r="D1314" t="n">
-        <v>41.76</v>
+        <v>41.7599983215332</v>
       </c>
       <c r="E1314" t="n">
-        <v>42.88</v>
+        <v>42.88000106811523</v>
       </c>
       <c r="F1314" t="n">
         <v>174276</v>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B1315" t="n">
+        <v>42.67</v>
+      </c>
+      <c r="C1315" t="n">
+        <v>42.74</v>
+      </c>
+      <c r="D1315" t="n">
+        <v>42.43</v>
+      </c>
+      <c r="E1315" t="n">
+        <v>42.55</v>
+      </c>
+      <c r="F1315" t="n">
+        <v>130699</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1315"/>
+  <dimension ref="A1:F1316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26712,19 +26712,39 @@
         <v>46233</v>
       </c>
       <c r="B1315" t="n">
-        <v>42.67</v>
+        <v>42.66999816894531</v>
       </c>
       <c r="C1315" t="n">
-        <v>42.74</v>
+        <v>42.7400016784668</v>
       </c>
       <c r="D1315" t="n">
-        <v>42.43</v>
+        <v>42.43000030517578</v>
       </c>
       <c r="E1315" t="n">
-        <v>42.55</v>
+        <v>42.54999923706055</v>
       </c>
       <c r="F1315" t="n">
         <v>130699</v>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B1316" t="n">
+        <v>41.48</v>
+      </c>
+      <c r="C1316" t="n">
+        <v>41.74</v>
+      </c>
+      <c r="D1316" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="E1316" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="F1316" t="n">
+        <v>188853</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1316"/>
+  <dimension ref="A1:F1317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26732,19 +26732,39 @@
         <v>46234</v>
       </c>
       <c r="B1316" t="n">
-        <v>41.48</v>
+        <v>41.47999954223633</v>
       </c>
       <c r="C1316" t="n">
-        <v>41.74</v>
+        <v>41.7400016784668</v>
       </c>
       <c r="D1316" t="n">
-        <v>41.3</v>
+        <v>41.29999923706055</v>
       </c>
       <c r="E1316" t="n">
         <v>41.5</v>
       </c>
       <c r="F1316" t="n">
         <v>188853</v>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B1317" t="n">
+        <v>42.45</v>
+      </c>
+      <c r="C1317" t="n">
+        <v>42.45</v>
+      </c>
+      <c r="D1317" t="n">
+        <v>41</v>
+      </c>
+      <c r="E1317" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="F1317" t="n">
+        <v>204182</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1317"/>
+  <dimension ref="A1:F1318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26752,10 +26752,10 @@
         <v>46237</v>
       </c>
       <c r="B1317" t="n">
-        <v>42.45</v>
+        <v>42.45000076293945</v>
       </c>
       <c r="C1317" t="n">
-        <v>42.45</v>
+        <v>42.45000076293945</v>
       </c>
       <c r="D1317" t="n">
         <v>41</v>
@@ -26765,6 +26765,26 @@
       </c>
       <c r="F1317" t="n">
         <v>204182</v>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B1318" t="n">
+        <v>42.58</v>
+      </c>
+      <c r="C1318" t="n">
+        <v>42.94</v>
+      </c>
+      <c r="D1318" t="n">
+        <v>42.01</v>
+      </c>
+      <c r="E1318" t="n">
+        <v>42.35</v>
+      </c>
+      <c r="F1318" t="n">
+        <v>235294</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1318"/>
+  <dimension ref="A1:F1319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26772,19 +26772,39 @@
         <v>46238</v>
       </c>
       <c r="B1318" t="n">
-        <v>42.58</v>
+        <v>42.58000183105469</v>
       </c>
       <c r="C1318" t="n">
-        <v>42.94</v>
+        <v>42.93999862670898</v>
       </c>
       <c r="D1318" t="n">
-        <v>42.01</v>
+        <v>42.0099983215332</v>
       </c>
       <c r="E1318" t="n">
-        <v>42.35</v>
+        <v>42.34999847412109</v>
       </c>
       <c r="F1318" t="n">
         <v>235294</v>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B1319" t="n">
+        <v>42.85</v>
+      </c>
+      <c r="C1319" t="n">
+        <v>43.15</v>
+      </c>
+      <c r="D1319" t="n">
+        <v>42.25</v>
+      </c>
+      <c r="E1319" t="n">
+        <v>42.31</v>
+      </c>
+      <c r="F1319" t="n">
+        <v>220653</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1319"/>
+  <dimension ref="A1:F1320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26792,19 +26792,39 @@
         <v>46239</v>
       </c>
       <c r="B1319" t="n">
-        <v>42.85</v>
+        <v>42.84999847412109</v>
       </c>
       <c r="C1319" t="n">
-        <v>43.15</v>
+        <v>43.15000152587891</v>
       </c>
       <c r="D1319" t="n">
         <v>42.25</v>
       </c>
       <c r="E1319" t="n">
-        <v>42.31</v>
+        <v>42.31000137329102</v>
       </c>
       <c r="F1319" t="n">
         <v>220653</v>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B1320" t="n">
+        <v>42.47</v>
+      </c>
+      <c r="C1320" t="n">
+        <v>42.85</v>
+      </c>
+      <c r="D1320" t="n">
+        <v>42.34</v>
+      </c>
+      <c r="E1320" t="n">
+        <v>42.65</v>
+      </c>
+      <c r="F1320" t="n">
+        <v>146162</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1320"/>
+  <dimension ref="A1:F1321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26812,19 +26812,39 @@
         <v>46240</v>
       </c>
       <c r="B1320" t="n">
-        <v>42.47</v>
+        <v>42.47000122070312</v>
       </c>
       <c r="C1320" t="n">
-        <v>42.85</v>
+        <v>42.84999847412109</v>
       </c>
       <c r="D1320" t="n">
-        <v>42.34</v>
+        <v>42.34000015258789</v>
       </c>
       <c r="E1320" t="n">
-        <v>42.65</v>
+        <v>42.65000152587891</v>
       </c>
       <c r="F1320" t="n">
         <v>146162</v>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B1321" t="n">
+        <v>42.35</v>
+      </c>
+      <c r="C1321" t="n">
+        <v>42.78</v>
+      </c>
+      <c r="D1321" t="n">
+        <v>42.13</v>
+      </c>
+      <c r="E1321" t="n">
+        <v>42.51</v>
+      </c>
+      <c r="F1321" t="n">
+        <v>138633</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1321"/>
+  <dimension ref="A1:F1322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26832,19 +26832,39 @@
         <v>46241</v>
       </c>
       <c r="B1321" t="n">
-        <v>42.35</v>
+        <v>42.34999847412109</v>
       </c>
       <c r="C1321" t="n">
-        <v>42.78</v>
+        <v>42.77999877929688</v>
       </c>
       <c r="D1321" t="n">
-        <v>42.13</v>
+        <v>42.13000106811523</v>
       </c>
       <c r="E1321" t="n">
-        <v>42.51</v>
+        <v>42.5099983215332</v>
       </c>
       <c r="F1321" t="n">
         <v>138633</v>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B1322" t="n">
+        <v>42.23</v>
+      </c>
+      <c r="C1322" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="D1322" t="n">
+        <v>41.98</v>
+      </c>
+      <c r="E1322" t="n">
+        <v>42.62</v>
+      </c>
+      <c r="F1322" t="n">
+        <v>140167</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1322"/>
+  <dimension ref="A1:F1323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26852,19 +26852,39 @@
         <v>46244</v>
       </c>
       <c r="B1322" t="n">
-        <v>42.23</v>
+        <v>42.22999954223633</v>
       </c>
       <c r="C1322" t="n">
-        <v>42.9</v>
+        <v>42.90000152587891</v>
       </c>
       <c r="D1322" t="n">
-        <v>41.98</v>
+        <v>41.97999954223633</v>
       </c>
       <c r="E1322" t="n">
-        <v>42.62</v>
+        <v>42.61999893188477</v>
       </c>
       <c r="F1322" t="n">
         <v>140167</v>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B1323" t="n">
+        <v>42.31</v>
+      </c>
+      <c r="C1323" t="n">
+        <v>42.31</v>
+      </c>
+      <c r="D1323" t="n">
+        <v>41.99</v>
+      </c>
+      <c r="E1323" t="n">
+        <v>42.23</v>
+      </c>
+      <c r="F1323" t="n">
+        <v>111270</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1323"/>
+  <dimension ref="A1:F1324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26872,19 +26872,39 @@
         <v>46245</v>
       </c>
       <c r="B1323" t="n">
-        <v>42.31</v>
+        <v>42.31000137329102</v>
       </c>
       <c r="C1323" t="n">
-        <v>42.31</v>
+        <v>42.31000137329102</v>
       </c>
       <c r="D1323" t="n">
-        <v>41.99</v>
+        <v>41.9900016784668</v>
       </c>
       <c r="E1323" t="n">
-        <v>42.23</v>
+        <v>42.22999954223633</v>
       </c>
       <c r="F1323" t="n">
         <v>111270</v>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B1324" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="C1324" t="n">
+        <v>42.73</v>
+      </c>
+      <c r="D1324" t="n">
+        <v>42.16</v>
+      </c>
+      <c r="E1324" t="n">
+        <v>42.61</v>
+      </c>
+      <c r="F1324" t="n">
+        <v>142831</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1324"/>
+  <dimension ref="A1:F1325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26892,19 +26892,39 @@
         <v>46246</v>
       </c>
       <c r="B1324" t="n">
-        <v>42.3</v>
+        <v>42.29999923706055</v>
       </c>
       <c r="C1324" t="n">
-        <v>42.73</v>
+        <v>42.72999954223633</v>
       </c>
       <c r="D1324" t="n">
-        <v>42.16</v>
+        <v>42.15999984741211</v>
       </c>
       <c r="E1324" t="n">
-        <v>42.61</v>
+        <v>42.61000061035156</v>
       </c>
       <c r="F1324" t="n">
         <v>142831</v>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B1325" t="n">
+        <v>42.46</v>
+      </c>
+      <c r="C1325" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="D1325" t="n">
+        <v>42.14</v>
+      </c>
+      <c r="E1325" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="F1325" t="n">
+        <v>118484</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1325"/>
+  <dimension ref="A1:F1326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26911,20 +26911,32 @@
       <c r="A1325" s="1" t="n">
         <v>46247</v>
       </c>
-      <c r="B1325" t="n">
+      <c r="B1325" t="inlineStr"/>
+      <c r="C1325" t="inlineStr"/>
+      <c r="D1325" t="inlineStr"/>
+      <c r="E1325" t="inlineStr"/>
+      <c r="F1325" t="n">
+        <v>121350</v>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B1326" t="n">
         <v>42.46</v>
       </c>
-      <c r="C1325" t="n">
-        <v>42.8</v>
-      </c>
-      <c r="D1325" t="n">
-        <v>42.14</v>
-      </c>
-      <c r="E1325" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="F1325" t="n">
-        <v>118484</v>
+      <c r="C1326" t="n">
+        <v>42.73</v>
+      </c>
+      <c r="D1326" t="n">
+        <v>42</v>
+      </c>
+      <c r="E1326" t="n">
+        <v>42.42</v>
+      </c>
+      <c r="F1326" t="n">
+        <v>121361</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1326"/>
+  <dimension ref="A1:F1327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26911,12 +26911,20 @@
       <c r="A1325" s="1" t="n">
         <v>46247</v>
       </c>
-      <c r="B1325" t="inlineStr"/>
-      <c r="C1325" t="inlineStr"/>
-      <c r="D1325" t="inlineStr"/>
-      <c r="E1325" t="inlineStr"/>
+      <c r="B1325" t="n">
+        <v>42.45999908447266</v>
+      </c>
+      <c r="C1325" t="n">
+        <v>42.79999923706055</v>
+      </c>
+      <c r="D1325" t="n">
+        <v>42.13999938964844</v>
+      </c>
+      <c r="E1325" t="n">
+        <v>42.5</v>
+      </c>
       <c r="F1325" t="n">
-        <v>121350</v>
+        <v>118484</v>
       </c>
     </row>
     <row r="1326">
@@ -26924,19 +26932,39 @@
         <v>46248</v>
       </c>
       <c r="B1326" t="n">
-        <v>42.46</v>
+        <v>42.45999908447266</v>
       </c>
       <c r="C1326" t="n">
-        <v>42.73</v>
+        <v>42.72999954223633</v>
       </c>
       <c r="D1326" t="n">
         <v>42</v>
       </c>
       <c r="E1326" t="n">
-        <v>42.42</v>
+        <v>42.41999816894531</v>
       </c>
       <c r="F1326" t="n">
         <v>121361</v>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B1327" t="n">
+        <v>43.07</v>
+      </c>
+      <c r="C1327" t="n">
+        <v>43.19</v>
+      </c>
+      <c r="D1327" t="n">
+        <v>42.31</v>
+      </c>
+      <c r="E1327" t="n">
+        <v>42.71</v>
+      </c>
+      <c r="F1327" t="n">
+        <v>152059</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1327"/>
+  <dimension ref="A1:F1328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26952,19 +26952,39 @@
         <v>46251</v>
       </c>
       <c r="B1327" t="n">
-        <v>43.07</v>
+        <v>43.06999969482422</v>
       </c>
       <c r="C1327" t="n">
-        <v>43.19</v>
+        <v>43.18999862670898</v>
       </c>
       <c r="D1327" t="n">
-        <v>42.31</v>
+        <v>42.31000137329102</v>
       </c>
       <c r="E1327" t="n">
-        <v>42.71</v>
+        <v>42.70999908447266</v>
       </c>
       <c r="F1327" t="n">
         <v>152059</v>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B1328" t="n">
+        <v>43.63</v>
+      </c>
+      <c r="C1328" t="n">
+        <v>43.63</v>
+      </c>
+      <c r="D1328" t="n">
+        <v>42.92</v>
+      </c>
+      <c r="E1328" t="n">
+        <v>43</v>
+      </c>
+      <c r="F1328" t="n">
+        <v>197985</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1328"/>
+  <dimension ref="A1:F1329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26971,20 +26971,32 @@
       <c r="A1328" s="1" t="n">
         <v>46252</v>
       </c>
-      <c r="B1328" t="n">
-        <v>43.63</v>
-      </c>
-      <c r="C1328" t="n">
-        <v>43.63</v>
-      </c>
-      <c r="D1328" t="n">
-        <v>42.92</v>
-      </c>
-      <c r="E1328" t="n">
-        <v>43</v>
-      </c>
+      <c r="B1328" t="inlineStr"/>
+      <c r="C1328" t="inlineStr"/>
+      <c r="D1328" t="inlineStr"/>
+      <c r="E1328" t="inlineStr"/>
       <c r="F1328" t="n">
-        <v>197985</v>
+        <v>525217</v>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B1329" t="n">
+        <v>45.95</v>
+      </c>
+      <c r="C1329" t="n">
+        <v>46.16</v>
+      </c>
+      <c r="D1329" t="n">
+        <v>43.19</v>
+      </c>
+      <c r="E1329" t="n">
+        <v>43.53</v>
+      </c>
+      <c r="F1329" t="n">
+        <v>535518</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1329"/>
+  <dimension ref="A1:F1330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26971,12 +26971,20 @@
       <c r="A1328" s="1" t="n">
         <v>46252</v>
       </c>
-      <c r="B1328" t="inlineStr"/>
-      <c r="C1328" t="inlineStr"/>
-      <c r="D1328" t="inlineStr"/>
-      <c r="E1328" t="inlineStr"/>
+      <c r="B1328" t="n">
+        <v>43.63000106811523</v>
+      </c>
+      <c r="C1328" t="n">
+        <v>43.63000106811523</v>
+      </c>
+      <c r="D1328" t="n">
+        <v>42.91999816894531</v>
+      </c>
+      <c r="E1328" t="n">
+        <v>43</v>
+      </c>
       <c r="F1328" t="n">
-        <v>525217</v>
+        <v>197985</v>
       </c>
     </row>
     <row r="1329">
@@ -26984,19 +26992,39 @@
         <v>46253</v>
       </c>
       <c r="B1329" t="n">
-        <v>45.95</v>
+        <v>45.95000076293945</v>
       </c>
       <c r="C1329" t="n">
-        <v>46.16</v>
+        <v>46.15999984741211</v>
       </c>
       <c r="D1329" t="n">
-        <v>43.19</v>
+        <v>43.18999862670898</v>
       </c>
       <c r="E1329" t="n">
-        <v>43.53</v>
+        <v>43.52999877929688</v>
       </c>
       <c r="F1329" t="n">
         <v>535518</v>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B1330" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="C1330" t="n">
+        <v>49.46</v>
+      </c>
+      <c r="D1330" t="n">
+        <v>48</v>
+      </c>
+      <c r="E1330" t="n">
+        <v>48.56</v>
+      </c>
+      <c r="F1330" t="n">
+        <v>484146</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1330"/>
+  <dimension ref="A1:F1331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27012,19 +27012,39 @@
         <v>46254</v>
       </c>
       <c r="B1330" t="n">
-        <v>49.1</v>
+        <v>49.09999847412109</v>
       </c>
       <c r="C1330" t="n">
-        <v>49.46</v>
+        <v>49.45999908447266</v>
       </c>
       <c r="D1330" t="n">
         <v>48</v>
       </c>
       <c r="E1330" t="n">
-        <v>48.56</v>
+        <v>48.56000137329102</v>
       </c>
       <c r="F1330" t="n">
         <v>484146</v>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B1331" t="n">
+        <v>51.54</v>
+      </c>
+      <c r="C1331" t="n">
+        <v>52.06</v>
+      </c>
+      <c r="D1331" t="n">
+        <v>50.93</v>
+      </c>
+      <c r="E1331" t="n">
+        <v>51.85</v>
+      </c>
+      <c r="F1331" t="n">
+        <v>564265</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1331"/>
+  <dimension ref="A1:F1332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27032,19 +27032,39 @@
         <v>46255</v>
       </c>
       <c r="B1331" t="n">
-        <v>51.54</v>
+        <v>51.54000091552734</v>
       </c>
       <c r="C1331" t="n">
-        <v>52.06</v>
+        <v>52.06000137329102</v>
       </c>
       <c r="D1331" t="n">
-        <v>50.93</v>
+        <v>50.93000030517578</v>
       </c>
       <c r="E1331" t="n">
-        <v>51.85</v>
+        <v>51.84999847412109</v>
       </c>
       <c r="F1331" t="n">
         <v>564265</v>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B1332" t="n">
+        <v>52.35</v>
+      </c>
+      <c r="C1332" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="D1332" t="n">
+        <v>51.79</v>
+      </c>
+      <c r="E1332" t="n">
+        <v>52.95</v>
+      </c>
+      <c r="F1332" t="n">
+        <v>644122</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1332"/>
+  <dimension ref="A1:F1333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27051,20 +27051,32 @@
       <c r="A1332" s="1" t="n">
         <v>46258</v>
       </c>
-      <c r="B1332" t="n">
-        <v>52.35</v>
-      </c>
-      <c r="C1332" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="D1332" t="n">
-        <v>51.79</v>
-      </c>
-      <c r="E1332" t="n">
+      <c r="B1332" t="inlineStr"/>
+      <c r="C1332" t="inlineStr"/>
+      <c r="D1332" t="inlineStr"/>
+      <c r="E1332" t="inlineStr"/>
+      <c r="F1332" t="n">
+        <v>434058</v>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B1333" t="n">
         <v>52.95</v>
       </c>
-      <c r="F1332" t="n">
-        <v>644122</v>
+      <c r="C1333" t="n">
+        <v>53.34</v>
+      </c>
+      <c r="D1333" t="n">
+        <v>52.39</v>
+      </c>
+      <c r="E1333" t="n">
+        <v>52.68</v>
+      </c>
+      <c r="F1333" t="n">
+        <v>436066</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1333"/>
+  <dimension ref="A1:F1334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27051,12 +27051,20 @@
       <c r="A1332" s="1" t="n">
         <v>46258</v>
       </c>
-      <c r="B1332" t="inlineStr"/>
-      <c r="C1332" t="inlineStr"/>
-      <c r="D1332" t="inlineStr"/>
-      <c r="E1332" t="inlineStr"/>
+      <c r="B1332" t="n">
+        <v>52.34999847412109</v>
+      </c>
+      <c r="C1332" t="n">
+        <v>53.09999847412109</v>
+      </c>
+      <c r="D1332" t="n">
+        <v>51.79000091552734</v>
+      </c>
+      <c r="E1332" t="n">
+        <v>52.95000076293945</v>
+      </c>
       <c r="F1332" t="n">
-        <v>434058</v>
+        <v>644122</v>
       </c>
     </row>
     <row r="1333">
@@ -27064,19 +27072,39 @@
         <v>46259</v>
       </c>
       <c r="B1333" t="n">
-        <v>52.95</v>
+        <v>52.95000076293945</v>
       </c>
       <c r="C1333" t="n">
-        <v>53.34</v>
+        <v>53.34000015258789</v>
       </c>
       <c r="D1333" t="n">
-        <v>52.39</v>
+        <v>52.38999938964844</v>
       </c>
       <c r="E1333" t="n">
-        <v>52.68</v>
+        <v>52.68000030517578</v>
       </c>
       <c r="F1333" t="n">
         <v>436066</v>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B1334" t="n">
+        <v>52.83000183105469</v>
+      </c>
+      <c r="C1334" t="n">
+        <v>52.95000076293945</v>
+      </c>
+      <c r="D1334" t="n">
+        <v>51.97999954223633</v>
+      </c>
+      <c r="E1334" t="n">
+        <v>52.75</v>
+      </c>
+      <c r="F1334" t="n">
+        <v>224459</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1334"/>
+  <dimension ref="A1:F1335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27104,7 +27104,27 @@
         <v>52.75</v>
       </c>
       <c r="F1334" t="n">
-        <v>224459</v>
+        <v>225750</v>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B1335" t="n">
+        <v>53.77</v>
+      </c>
+      <c r="C1335" t="n">
+        <v>54.55</v>
+      </c>
+      <c r="D1335" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="E1335" t="n">
+        <v>53.32</v>
+      </c>
+      <c r="F1335" t="n">
+        <v>351674</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1335"/>
+  <dimension ref="A1:F1336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27111,20 +27111,32 @@
       <c r="A1335" s="1" t="n">
         <v>46261</v>
       </c>
-      <c r="B1335" t="n">
-        <v>53.77</v>
-      </c>
-      <c r="C1335" t="n">
-        <v>54.55</v>
-      </c>
-      <c r="D1335" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="E1335" t="n">
-        <v>53.32</v>
-      </c>
+      <c r="B1335" t="inlineStr"/>
+      <c r="C1335" t="inlineStr"/>
+      <c r="D1335" t="inlineStr"/>
+      <c r="E1335" t="inlineStr"/>
       <c r="F1335" t="n">
-        <v>351674</v>
+        <v>195433</v>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B1336" t="n">
+        <v>51.81</v>
+      </c>
+      <c r="C1336" t="n">
+        <v>53.92</v>
+      </c>
+      <c r="D1336" t="n">
+        <v>51.76</v>
+      </c>
+      <c r="E1336" t="n">
+        <v>53.63</v>
+      </c>
+      <c r="F1336" t="n">
+        <v>195417</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -27116,7 +27116,7 @@
       <c r="D1335" t="inlineStr"/>
       <c r="E1335" t="inlineStr"/>
       <c r="F1335" t="n">
-        <v>195433</v>
+        <v>298840</v>
       </c>
     </row>
     <row r="1336">
@@ -27124,7 +27124,7 @@
         <v>46262</v>
       </c>
       <c r="B1336" t="n">
-        <v>51.81</v>
+        <v>51.91</v>
       </c>
       <c r="C1336" t="n">
         <v>53.92</v>
@@ -27136,7 +27136,7 @@
         <v>53.63</v>
       </c>
       <c r="F1336" t="n">
-        <v>195417</v>
+        <v>298840</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1336"/>
+  <dimension ref="A1:F1335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27109,7 +27109,7 @@
     </row>
     <row r="1335">
       <c r="A1335" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B1335" t="inlineStr"/>
       <c r="C1335" t="inlineStr"/>
@@ -27119,26 +27119,6 @@
         <v>298840</v>
       </c>
     </row>
-    <row r="1336">
-      <c r="A1336" s="1" t="n">
-        <v>46262</v>
-      </c>
-      <c r="B1336" t="n">
-        <v>51.91</v>
-      </c>
-      <c r="C1336" t="n">
-        <v>53.92</v>
-      </c>
-      <c r="D1336" t="n">
-        <v>51.76</v>
-      </c>
-      <c r="E1336" t="n">
-        <v>53.63</v>
-      </c>
-      <c r="F1336" t="n">
-        <v>298840</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1335"/>
+  <dimension ref="A1:F1338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27109,14 +27109,82 @@
     </row>
     <row r="1335">
       <c r="A1335" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B1335" t="n">
+        <v>53.77000045776367</v>
+      </c>
+      <c r="C1335" t="n">
+        <v>54.54999923706055</v>
+      </c>
+      <c r="D1335" t="n">
+        <v>53.09999847412109</v>
+      </c>
+      <c r="E1335" t="n">
+        <v>53.31999969482422</v>
+      </c>
+      <c r="F1335" t="n">
+        <v>351674</v>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" s="1" t="n">
         <v>46262</v>
       </c>
-      <c r="B1335" t="inlineStr"/>
-      <c r="C1335" t="inlineStr"/>
-      <c r="D1335" t="inlineStr"/>
-      <c r="E1335" t="inlineStr"/>
-      <c r="F1335" t="n">
-        <v>298840</v>
+      <c r="B1336" t="n">
+        <v>51.90999984741211</v>
+      </c>
+      <c r="C1336" t="n">
+        <v>53.91999816894531</v>
+      </c>
+      <c r="D1336" t="n">
+        <v>51.7599983215332</v>
+      </c>
+      <c r="E1336" t="n">
+        <v>53.63000106811523</v>
+      </c>
+      <c r="F1336" t="n">
+        <v>300731</v>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B1337" t="n">
+        <v>53.31999969482422</v>
+      </c>
+      <c r="C1337" t="n">
+        <v>53.63999938964844</v>
+      </c>
+      <c r="D1337" t="n">
+        <v>51.70000076293945</v>
+      </c>
+      <c r="E1337" t="n">
+        <v>52.41999816894531</v>
+      </c>
+      <c r="F1337" t="n">
+        <v>194555</v>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B1338" t="n">
+        <v>51.75</v>
+      </c>
+      <c r="C1338" t="n">
+        <v>52.75</v>
+      </c>
+      <c r="D1338" t="n">
+        <v>51.34</v>
+      </c>
+      <c r="E1338" t="n">
+        <v>52.75</v>
+      </c>
+      <c r="F1338" t="n">
+        <v>236199</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1338"/>
+  <dimension ref="A1:F1339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27171,20 +27171,32 @@
       <c r="A1338" s="1" t="n">
         <v>46266</v>
       </c>
-      <c r="B1338" t="n">
+      <c r="B1338" t="inlineStr"/>
+      <c r="C1338" t="inlineStr"/>
+      <c r="D1338" t="inlineStr"/>
+      <c r="E1338" t="inlineStr"/>
+      <c r="F1338" t="n">
+        <v>206840</v>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B1339" t="n">
+        <v>51.45</v>
+      </c>
+      <c r="C1339" t="n">
         <v>51.75</v>
       </c>
-      <c r="C1338" t="n">
-        <v>52.75</v>
-      </c>
-      <c r="D1338" t="n">
-        <v>51.34</v>
-      </c>
-      <c r="E1338" t="n">
-        <v>52.75</v>
-      </c>
-      <c r="F1338" t="n">
-        <v>236199</v>
+      <c r="D1339" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="E1339" t="n">
+        <v>51.67</v>
+      </c>
+      <c r="F1339" t="n">
+        <v>207451</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1339"/>
+  <dimension ref="A1:F1340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27171,12 +27171,20 @@
       <c r="A1338" s="1" t="n">
         <v>46266</v>
       </c>
-      <c r="B1338" t="inlineStr"/>
-      <c r="C1338" t="inlineStr"/>
-      <c r="D1338" t="inlineStr"/>
-      <c r="E1338" t="inlineStr"/>
+      <c r="B1338" t="n">
+        <v>51.75</v>
+      </c>
+      <c r="C1338" t="n">
+        <v>52.75</v>
+      </c>
+      <c r="D1338" t="n">
+        <v>51.34000015258789</v>
+      </c>
+      <c r="E1338" t="n">
+        <v>52.75</v>
+      </c>
       <c r="F1338" t="n">
-        <v>206840</v>
+        <v>236199</v>
       </c>
     </row>
     <row r="1339">
@@ -27184,19 +27192,39 @@
         <v>46267</v>
       </c>
       <c r="B1339" t="n">
-        <v>51.45</v>
+        <v>51.45000076293945</v>
       </c>
       <c r="C1339" t="n">
         <v>51.75</v>
       </c>
       <c r="D1339" t="n">
-        <v>50.8</v>
+        <v>50.79999923706055</v>
       </c>
       <c r="E1339" t="n">
-        <v>51.67</v>
+        <v>51.66999816894531</v>
       </c>
       <c r="F1339" t="n">
         <v>207451</v>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B1340" t="n">
+        <v>54.03</v>
+      </c>
+      <c r="C1340" t="n">
+        <v>54.03</v>
+      </c>
+      <c r="D1340" t="n">
+        <v>51.96</v>
+      </c>
+      <c r="E1340" t="n">
+        <v>52.01</v>
+      </c>
+      <c r="F1340" t="n">
+        <v>284520</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1340"/>
+  <dimension ref="A1:F1341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27211,20 +27211,32 @@
       <c r="A1340" s="1" t="n">
         <v>46268</v>
       </c>
-      <c r="B1340" t="n">
-        <v>54.03</v>
-      </c>
-      <c r="C1340" t="n">
-        <v>54.03</v>
-      </c>
-      <c r="D1340" t="n">
-        <v>51.96</v>
-      </c>
-      <c r="E1340" t="n">
-        <v>52.01</v>
-      </c>
+      <c r="B1340" t="inlineStr"/>
+      <c r="C1340" t="inlineStr"/>
+      <c r="D1340" t="inlineStr"/>
+      <c r="E1340" t="inlineStr"/>
       <c r="F1340" t="n">
-        <v>284520</v>
+        <v>204751</v>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B1341" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="C1341" t="n">
+        <v>53.19</v>
+      </c>
+      <c r="D1341" t="n">
+        <v>52.25</v>
+      </c>
+      <c r="E1341" t="n">
+        <v>53.19</v>
+      </c>
+      <c r="F1341" t="n">
+        <v>205073</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -27211,12 +27211,20 @@
       <c r="A1340" s="1" t="n">
         <v>46268</v>
       </c>
-      <c r="B1340" t="inlineStr"/>
-      <c r="C1340" t="inlineStr"/>
-      <c r="D1340" t="inlineStr"/>
-      <c r="E1340" t="inlineStr"/>
+      <c r="B1340" t="n">
+        <v>54.02999877929688</v>
+      </c>
+      <c r="C1340" t="n">
+        <v>54.02999877929688</v>
+      </c>
+      <c r="D1340" t="n">
+        <v>51.95999908447266</v>
+      </c>
+      <c r="E1340" t="n">
+        <v>52.0099983215332</v>
+      </c>
       <c r="F1340" t="n">
-        <v>204751</v>
+        <v>284520</v>
       </c>
     </row>
     <row r="1341">
@@ -27224,16 +27232,16 @@
         <v>46269</v>
       </c>
       <c r="B1341" t="n">
-        <v>53.1</v>
+        <v>53.09999847412109</v>
       </c>
       <c r="C1341" t="n">
-        <v>53.19</v>
+        <v>53.18999862670898</v>
       </c>
       <c r="D1341" t="n">
         <v>52.25</v>
       </c>
       <c r="E1341" t="n">
-        <v>53.19</v>
+        <v>53.18999862670898</v>
       </c>
       <c r="F1341" t="n">
         <v>205073</v>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1341"/>
+  <dimension ref="A1:F1342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27247,6 +27247,26 @@
         <v>205073</v>
       </c>
     </row>
+    <row r="1342">
+      <c r="A1342" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B1342" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="C1342" t="n">
+        <v>52.66</v>
+      </c>
+      <c r="D1342" t="n">
+        <v>51.48</v>
+      </c>
+      <c r="E1342" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="F1342" t="n">
+        <v>256241</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1342"/>
+  <dimension ref="A1:F1343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27267,6 +27267,26 @@
         <v>256241</v>
       </c>
     </row>
+    <row r="1343">
+      <c r="A1343" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B1343" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="C1343" t="n">
+        <v>53</v>
+      </c>
+      <c r="D1343" t="n">
+        <v>52.18</v>
+      </c>
+      <c r="E1343" t="n">
+        <v>52.92</v>
+      </c>
+      <c r="F1343" t="n">
+        <v>183624</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1343"/>
+  <dimension ref="A1:F1344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27252,13 +27252,13 @@
         <v>46273</v>
       </c>
       <c r="B1342" t="n">
-        <v>52.1</v>
+        <v>52.09999847412109</v>
       </c>
       <c r="C1342" t="n">
-        <v>52.66</v>
+        <v>52.65999984741211</v>
       </c>
       <c r="D1342" t="n">
-        <v>51.48</v>
+        <v>51.47999954223633</v>
       </c>
       <c r="E1342" t="n">
         <v>52.5</v>
@@ -27272,19 +27272,39 @@
         <v>46274</v>
       </c>
       <c r="B1343" t="n">
-        <v>52.3</v>
+        <v>52.29999923706055</v>
       </c>
       <c r="C1343" t="n">
         <v>53</v>
       </c>
       <c r="D1343" t="n">
-        <v>52.18</v>
+        <v>52.18000030517578</v>
       </c>
       <c r="E1343" t="n">
-        <v>52.92</v>
+        <v>52.91999816894531</v>
       </c>
       <c r="F1343" t="n">
         <v>183624</v>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B1344" t="n">
+        <v>51.49</v>
+      </c>
+      <c r="C1344" t="n">
+        <v>51.95</v>
+      </c>
+      <c r="D1344" t="n">
+        <v>51.19</v>
+      </c>
+      <c r="E1344" t="n">
+        <v>51.83</v>
+      </c>
+      <c r="F1344" t="n">
+        <v>170003</v>
       </c>
     </row>
   </sheetData>

--- a/database/HASH11.xlsx
+++ b/database/HASH11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1344"/>
+  <dimension ref="A1:F1345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27292,19 +27292,39 @@
         <v>46275</v>
       </c>
       <c r="B1344" t="n">
-        <v>51.49</v>
+        <v>51.4900016784668</v>
       </c>
       <c r="C1344" t="n">
-        <v>51.95</v>
+        <v>51.95000076293945</v>
       </c>
       <c r="D1344" t="n">
-        <v>51.19</v>
+        <v>51.18999862670898</v>
       </c>
       <c r="E1344" t="n">
-        <v>51.83</v>
+        <v>51.83000183105469</v>
       </c>
       <c r="F1344" t="n">
         <v>170003</v>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B1345" t="n">
+        <v>51.98</v>
+      </c>
+      <c r="C1345" t="n">
+        <v>53.37</v>
+      </c>
+      <c r="D1345" t="n">
+        <v>51.49</v>
+      </c>
+      <c r="E1345" t="n">
+        <v>51.49</v>
+      </c>
+      <c r="F1345" t="n">
+        <v>201437</v>
       </c>
     </row>
   </sheetData>
